--- a/notes/Leetcode 官方题解/刷题清单.xlsx
+++ b/notes/Leetcode 官方题解/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
   <si>
     <t>编号</t>
   </si>
@@ -197,6 +197,18 @@
   </si>
   <si>
     <t>双栈模拟</t>
+  </si>
+  <si>
+    <t>分割回文串</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning/</t>
+  </si>
+  <si>
+    <t>回溯+动态规划</t>
+  </si>
+  <si>
+    <t>动态规划/记忆化搜索降低判断回文数的复杂度</t>
   </si>
 </sst>
 </file>
@@ -204,8 +216,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -230,6 +242,119 @@
       <charset val="134"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -238,75 +363,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -320,59 +379,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -401,181 +413,181 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -604,17 +616,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -624,15 +639,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,6 +658,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -667,11 +688,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -686,21 +713,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -709,10 +721,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -721,137 +733,137 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -889,6 +901,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1242,16 +1257,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
     <col min="2" max="2" width="23.375" style="4" customWidth="1"/>
     <col min="3" max="3" width="28.125" style="4" customWidth="1"/>
-    <col min="4" max="4" width="5.125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12.875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="6.5" style="4" customWidth="1"/>
+    <col min="5" max="5" width="15.125" style="4" customWidth="1"/>
     <col min="6" max="7" width="5.125" style="4" customWidth="1"/>
-    <col min="8" max="8" width="37" style="4" customWidth="1"/>
+    <col min="8" max="8" width="41.125" style="4" customWidth="1"/>
     <col min="9" max="16383" width="18.625" style="4" customWidth="1"/>
     <col min="16384" max="16384" width="18.625" style="4"/>
   </cols>
@@ -1739,14 +1754,30 @@
       <c r="H26" s="11"/>
     </row>
     <row r="27" spans="1:8">
-      <c r="A27" s="5"/>
-      <c r="B27" s="6"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="A27" s="5">
+        <v>232</v>
+      </c>
+      <c r="B27" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="5">
+        <v>1</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="5"/>
@@ -1789,30 +1820,14 @@
       <c r="H31" s="5"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="5">
-        <v>232</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="G32" s="5">
-        <v>1</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>59</v>
-      </c>
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="5"/>
@@ -1836,13 +1851,79 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="5"/>
-      <c r="B35" s="5"/>
+      <c r="B35" s="6"/>
       <c r="C35" s="5"/>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="5"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="5"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="5"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="5">
+        <v>131</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G39" s="5">
+        <v>1</v>
+      </c>
+      <c r="H39" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H7">
@@ -1863,7 +1944,8 @@
     <hyperlink ref="B21" r:id="rId11" display="二叉树的最大深度" tooltip="https://leetcode-cn.com/problems/maximum-depth-of-binary-tree/"/>
     <hyperlink ref="B25" r:id="rId12" display="比特位计数" tooltip="https://leetcode-cn.com/problems/counting-bits/"/>
     <hyperlink ref="B26" r:id="rId13" display="删除排序数组中的重复项" tooltip="https://leetcode-cn.com/problems/remove-duplicates-from-sorted-array/"/>
-    <hyperlink ref="B32" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B27" r:id="rId14" display="用栈实现队列" tooltip="https://leetcode-cn.com/problems/implement-queue-using-stacks/"/>
+    <hyperlink ref="B39" r:id="rId15" display="分割回文串" tooltip="https://leetcode-cn.com/problems/palindrome-partitioning/"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/notes/Leetcode 官方题解/刷题清单.xlsx
+++ b/notes/Leetcode 官方题解/刷题清单.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="68">
   <si>
     <t>编号</t>
   </si>
@@ -209,6 +209,18 @@
   </si>
   <si>
     <t>动态规划/记忆化搜索降低判断回文数的复杂度</t>
+  </si>
+  <si>
+    <t>分割回文串 II</t>
+  </si>
+  <si>
+    <t>https://leetcode-cn.com/problems/palindrome-partitioning-ii/</t>
+  </si>
+  <si>
+    <t>困难</t>
+  </si>
+  <si>
+    <t>动态规划/记忆化搜索</t>
   </si>
 </sst>
 </file>
@@ -906,7 +918,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1257,7 +1269,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr defaultColWidth="18.625" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="5.375" style="4" customWidth="1"/>
@@ -1900,7 +1912,7 @@
         <v>61</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>62</v>
@@ -1916,14 +1928,40 @@
       </c>
     </row>
     <row r="40" spans="1:8">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
+      <c r="A40" s="5">
+        <v>132</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="5">
+        <v>1</v>
+      </c>
+      <c r="H40" s="5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" s="5"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:H7">
